--- a/storage/app/public/generated/SF2/SF2_2024-2025_11_Alexandrite and Diamond_3_2026.xlsx
+++ b/storage/app/public/generated/SF2/SF2_2024-2025_11_Alexandrite and Diamond_3_2026.xlsx
@@ -226,6 +226,9 @@
     <t>DE GUZMAN,ROBINO JR. MAMARIL</t>
   </si>
   <si>
+    <t>Dela Cruz, Juan JR M.</t>
+  </si>
+  <si>
     <t>DOMINGO,JOHN CARLO GUIANG</t>
   </si>
   <si>
@@ -247,9 +250,6 @@
     <t>PONCE,DOMINGO TORRES</t>
   </si>
   <si>
-    <t>SANCHEZ,RHEY LAURENZ MANALO</t>
-  </si>
-  <si>
     <t>MALE  | TOTAL Per Day</t>
   </si>
   <si>
@@ -271,10 +271,10 @@
     <t>Rodriguez, Ana C.</t>
   </si>
   <si>
+    <t>Santos, Maria C.</t>
+  </si>
+  <si>
     <t>SUBANG,DIANNA JANE CRISTOBAL</t>
-  </si>
-  <si>
-    <t>Santos, Maria C.</t>
   </si>
   <si>
     <t xml:space="preserve">            FEMALE  | DAILY TOTAL </t>
@@ -516,7 +516,7 @@
        feuds)</t>
   </si>
   <si>
-    <t>Regielyn P.Gaspar</t>
+    <t>Regielyn P. Gaspar</t>
   </si>
   <si>
     <t xml:space="preserve">                          (Signature of Teacher over Printed Name)</t>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="13" spans="1:37" customHeight="1" ht="21.9">
       <c r="A13" s="56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B13" s="259" t="s">
         <v>23</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="14" spans="1:37" customHeight="1" ht="21.9">
       <c r="A14" s="11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B14" s="261" t="s">
         <v>24</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="15" spans="1:37" customHeight="1" ht="21.9">
       <c r="A15" s="56">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B15" s="261" t="s">
         <v>25</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="16" spans="1:37" customHeight="1" ht="21.9">
       <c r="A16" s="11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B16" s="261" t="s">
         <v>26</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="17" spans="1:37" customHeight="1" ht="21.9">
       <c r="A17" s="56">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B17" s="261" t="s">
         <v>27</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="18" spans="1:37" customHeight="1" ht="21.9">
       <c r="A18" s="11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B18" s="261" t="s">
         <v>29</v>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="19" spans="1:37" customHeight="1" ht="21.9">
       <c r="A19" s="56">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B19" s="261" t="s">
         <v>30</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="20" spans="1:37" customHeight="1" ht="21.9">
       <c r="A20" s="11">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B20" s="261" t="s">
         <v>31</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="21" spans="1:37" customHeight="1" ht="21.9">
       <c r="A21" s="56">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B21" s="261" t="s">
         <v>32</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="22" spans="1:37" customHeight="1" ht="21.9">
       <c r="A22" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B22" s="261" t="s">
         <v>33</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="23" spans="1:37" customHeight="1" ht="21.9">
       <c r="A23" s="56">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B23" s="261" t="s">
         <v>34</v>
@@ -4213,7 +4213,7 @@
     </row>
     <row r="24" spans="1:37" customHeight="1" ht="21.9">
       <c r="A24" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B24" s="263" t="s">
         <v>35</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="25" spans="1:37" customHeight="1" ht="21.9">
       <c r="A25" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B25" s="263" t="s">
         <v>36</v>
@@ -4307,39 +4307,83 @@
     </row>
     <row r="26" spans="1:37" customHeight="1" ht="21.9">
       <c r="A26" s="11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B26" s="263" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="264"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="64"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="67"/>
-      <c r="X26" s="68"/>
-      <c r="Y26" s="66"/>
+      <c r="D26" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="R26" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="S26" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="T26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="U26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="V26" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="W26" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="X26" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y26" s="66" t="s">
+        <v>28</v>
+      </c>
       <c r="Z26" s="66"/>
       <c r="AA26" s="67"/>
       <c r="AB26" s="67"/>
       <c r="AC26" s="118">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AD26" s="108">
         <v>0</v>
@@ -4353,7 +4397,7 @@
     </row>
     <row r="27" spans="1:37" customHeight="1" ht="21.9">
       <c r="A27" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B27" s="263" t="s">
         <v>38</v>
@@ -4367,9 +4411,7 @@
       <c r="I27" s="65"/>
       <c r="J27" s="66"/>
       <c r="K27" s="66"/>
-      <c r="L27" s="66" t="s">
-        <v>28</v>
-      </c>
+      <c r="L27" s="66"/>
       <c r="M27" s="67"/>
       <c r="N27" s="68"/>
       <c r="O27" s="66"/>
@@ -4387,7 +4429,7 @@
       <c r="AA27" s="67"/>
       <c r="AB27" s="67"/>
       <c r="AC27" s="118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="108">
         <v>0</v>
@@ -4401,7 +4443,7 @@
     </row>
     <row r="28" spans="1:37" customHeight="1" ht="21.9">
       <c r="A28" s="11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B28" s="263" t="s">
         <v>39</v>
@@ -4415,7 +4457,9 @@
       <c r="I28" s="72"/>
       <c r="J28" s="70"/>
       <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
+      <c r="L28" s="70" t="s">
+        <v>28</v>
+      </c>
       <c r="M28" s="73"/>
       <c r="N28" s="69"/>
       <c r="O28" s="70"/>
@@ -4433,7 +4477,7 @@
       <c r="AA28" s="73"/>
       <c r="AB28" s="73"/>
       <c r="AC28" s="119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" s="120">
         <v>0</v>
@@ -4447,7 +4491,7 @@
     </row>
     <row r="29" spans="1:37" customHeight="1" ht="21.9">
       <c r="A29" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B29" s="263" t="s">
         <v>40</v>
@@ -4493,7 +4537,7 @@
     </row>
     <row r="30" spans="1:37" customHeight="1" ht="21.9">
       <c r="A30" s="11">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B30" s="263" t="s">
         <v>41</v>
@@ -4506,9 +4550,7 @@
       <c r="H30" s="71"/>
       <c r="I30" s="72"/>
       <c r="J30" s="70"/>
-      <c r="K30" s="70" t="s">
-        <v>28</v>
-      </c>
+      <c r="K30" s="70"/>
       <c r="L30" s="70"/>
       <c r="M30" s="73"/>
       <c r="N30" s="69"/>
@@ -4522,14 +4564,12 @@
       <c r="V30" s="70"/>
       <c r="W30" s="73"/>
       <c r="X30" s="69"/>
-      <c r="Y30" s="70" t="s">
-        <v>28</v>
-      </c>
+      <c r="Y30" s="70"/>
       <c r="Z30" s="70"/>
       <c r="AA30" s="73"/>
       <c r="AB30" s="73"/>
       <c r="AC30" s="119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="120">
         <v>0</v>
@@ -4543,7 +4583,7 @@
     </row>
     <row r="31" spans="1:37" customHeight="1" ht="21.9">
       <c r="A31" s="11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B31" s="263" t="s">
         <v>42</v>
@@ -4552,23 +4592,19 @@
       <c r="D31" s="69"/>
       <c r="E31" s="70"/>
       <c r="F31" s="70"/>
-      <c r="G31" s="70" t="s">
-        <v>28</v>
-      </c>
+      <c r="G31" s="70"/>
       <c r="H31" s="71"/>
       <c r="I31" s="72"/>
       <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
+      <c r="K31" s="70" t="s">
+        <v>28</v>
+      </c>
       <c r="L31" s="70"/>
-      <c r="M31" s="73" t="s">
-        <v>28</v>
-      </c>
+      <c r="M31" s="73"/>
       <c r="N31" s="69"/>
       <c r="O31" s="70"/>
       <c r="P31" s="70"/>
-      <c r="Q31" s="70" t="s">
-        <v>28</v>
-      </c>
+      <c r="Q31" s="70"/>
       <c r="R31" s="71"/>
       <c r="S31" s="72"/>
       <c r="T31" s="70"/>
@@ -4576,12 +4612,14 @@
       <c r="V31" s="70"/>
       <c r="W31" s="73"/>
       <c r="X31" s="69"/>
-      <c r="Y31" s="70"/>
+      <c r="Y31" s="70" t="s">
+        <v>28</v>
+      </c>
       <c r="Z31" s="70"/>
       <c r="AA31" s="73"/>
       <c r="AB31" s="73"/>
       <c r="AC31" s="119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD31" s="120">
         <v>0</v>
@@ -4595,7 +4633,7 @@
     </row>
     <row r="32" spans="1:37" customHeight="1" ht="21.9">
       <c r="A32" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B32" s="263" t="s">
         <v>43</v>
@@ -4604,34 +4642,36 @@
       <c r="D32" s="69"/>
       <c r="E32" s="70"/>
       <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
+      <c r="G32" s="70" t="s">
+        <v>28</v>
+      </c>
       <c r="H32" s="71"/>
       <c r="I32" s="72"/>
       <c r="J32" s="70"/>
       <c r="K32" s="70"/>
       <c r="L32" s="70"/>
-      <c r="M32" s="73"/>
+      <c r="M32" s="73" t="s">
+        <v>28</v>
+      </c>
       <c r="N32" s="69"/>
       <c r="O32" s="70"/>
-      <c r="P32" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70" t="s">
+        <v>28</v>
+      </c>
       <c r="R32" s="71"/>
       <c r="S32" s="72"/>
       <c r="T32" s="70"/>
       <c r="U32" s="70"/>
       <c r="V32" s="70"/>
       <c r="W32" s="73"/>
-      <c r="X32" s="69" t="s">
-        <v>28</v>
-      </c>
+      <c r="X32" s="69"/>
       <c r="Y32" s="70"/>
       <c r="Z32" s="70"/>
       <c r="AA32" s="73"/>
       <c r="AB32" s="73"/>
       <c r="AC32" s="119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD32" s="120">
         <v>0</v>
@@ -4645,7 +4685,7 @@
     </row>
     <row r="33" spans="1:37" customHeight="1" ht="21.9">
       <c r="A33" s="74">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B33" s="265" t="s">
         <v>44</v>
@@ -4663,7 +4703,9 @@
       <c r="M33" s="79"/>
       <c r="N33" s="75"/>
       <c r="O33" s="76"/>
-      <c r="P33" s="76"/>
+      <c r="P33" s="76" t="s">
+        <v>28</v>
+      </c>
       <c r="Q33" s="76"/>
       <c r="R33" s="77"/>
       <c r="S33" s="78"/>
@@ -4671,13 +4713,15 @@
       <c r="U33" s="76"/>
       <c r="V33" s="76"/>
       <c r="W33" s="79"/>
-      <c r="X33" s="75"/>
+      <c r="X33" s="75" t="s">
+        <v>28</v>
+      </c>
       <c r="Y33" s="76"/>
       <c r="Z33" s="76"/>
       <c r="AA33" s="79"/>
       <c r="AB33" s="79"/>
       <c r="AC33" s="121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD33" s="110">
         <v>0</v>
@@ -4697,97 +4741,97 @@
       <c r="C34" s="125"/>
       <c r="D34" s="112">
         <f>COUNTIF(D13:D33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="113">
         <f>COUNTIF(E13:E33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="113">
         <f>COUNTIF(F13:F33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="113">
         <f>COUNTIF(G13:G33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="114">
         <f>COUNTIF(H13:H33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="115">
         <f>COUNTIF(I13:I33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="113">
         <f>COUNTIF(J13:J33,"x")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="113">
         <f>COUNTIF(K13:K33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="113">
         <f>COUNTIF(L13:L33,"x")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="116">
         <f>COUNTIF(M13:M33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="112">
         <f>COUNTIF(N13:N33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="113">
         <f>COUNTIF(O13:O33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="113">
         <f>COUNTIF(P13:P33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="113">
         <f>COUNTIF(Q13:Q33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" s="114">
         <f>COUNTIF(R13:R33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" s="115">
         <f>COUNTIF(S13:S33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="113">
         <f>COUNTIF(T13:T33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="113">
         <f>COUNTIF(U13:U33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34" s="113">
         <f>COUNTIF(V13:V33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="116">
         <f>COUNTIF(W13:W33,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="112">
         <f>COUNTIF(X13:X33,"x")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y34" s="113">
         <f>COUNTIF(Y13:Y33,"x")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="113"/>
       <c r="AA34" s="116"/>
       <c r="AB34" s="116"/>
       <c r="AC34" s="122">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AD34" s="111">
         <v>0</v>
@@ -5041,7 +5085,7 @@
     </row>
     <row r="40" spans="1:37" customHeight="1" ht="21.9">
       <c r="A40" s="11">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B40" s="267" t="s">
         <v>51</v>
@@ -5131,41 +5175,83 @@
     </row>
     <row r="41" spans="1:37" customHeight="1" ht="21.9">
       <c r="A41" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" s="267" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="268"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="68"/>
-      <c r="O41" s="66"/>
-      <c r="P41" s="66"/>
-      <c r="Q41" s="66"/>
-      <c r="R41" s="64"/>
-      <c r="S41" s="65"/>
-      <c r="T41" s="66"/>
-      <c r="U41" s="66"/>
+      <c r="D41" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="M41" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="R41" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="S41" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="T41" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="U41" s="66" t="s">
+        <v>28</v>
+      </c>
       <c r="V41" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="W41" s="67"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="66"/>
+      <c r="W41" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="X41" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y41" s="66" t="s">
+        <v>28</v>
+      </c>
       <c r="Z41" s="66"/>
       <c r="AA41" s="67"/>
       <c r="AB41" s="67"/>
       <c r="AC41" s="118">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="AD41" s="108">
         <v>0</v>
@@ -5179,83 +5265,41 @@
     </row>
     <row r="42" spans="1:37" customHeight="1" ht="21.9">
       <c r="A42" s="11">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B42" s="267" t="s">
         <v>53</v>
       </c>
       <c r="C42" s="268"/>
-      <c r="D42" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G42" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="L42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="M42" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="P42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="R42" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="S42" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="T42" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="U42" s="66" t="s">
-        <v>28</v>
-      </c>
+      <c r="D42" s="47"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="66"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="68"/>
+      <c r="O42" s="66"/>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="64"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="66"/>
+      <c r="U42" s="66"/>
       <c r="V42" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="W42" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="X42" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y42" s="66" t="s">
-        <v>28</v>
-      </c>
+      <c r="W42" s="67"/>
+      <c r="X42" s="68"/>
+      <c r="Y42" s="66"/>
       <c r="Z42" s="66"/>
       <c r="AA42" s="67"/>
       <c r="AB42" s="67"/>
       <c r="AC42" s="118">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AD42" s="108">
         <v>0</v>
@@ -6031,97 +6075,97 @@
       <c r="C61" s="211"/>
       <c r="D61" s="99">
         <f>D34+D60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="100">
         <f>E34+E60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="100">
         <f>F34+F60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" s="100">
         <f>G34+G60</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H61" s="101">
         <f>H34+H60</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61" s="102">
         <f>I34+I60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" s="100">
         <f>J34+J60</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K61" s="100">
         <f>K34+K60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L61" s="100">
         <f>L34+L60</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61" s="103">
         <f>M34+M60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N61" s="99">
         <f>N34+N60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O61" s="100">
         <f>O34+O60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P61" s="100">
         <f>P34+P60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q61" s="100">
         <f>Q34+Q60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R61" s="101">
         <f>R34+R60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61" s="102">
         <f>S34+S60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" s="100">
         <f>T34+T60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U61" s="100">
         <f>U34+U60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V61" s="100">
         <f>V34+V60</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W61" s="103">
         <f>W34+W60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X61" s="99">
         <f>X34+X60</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y61" s="100">
         <f>Y34+Y60</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z61" s="100"/>
       <c r="AA61" s="103"/>
       <c r="AB61" s="103"/>
       <c r="AC61" s="122">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="AD61" s="111">
         <v>0</v>
@@ -6280,13 +6324,13 @@
       <c r="AF65" s="143"/>
       <c r="AG65" s="144"/>
       <c r="AH65" s="135">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI65" s="135">
         <v>8</v>
       </c>
       <c r="AJ65" s="223">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:37" customHeight="1" ht="15.75">
@@ -6458,13 +6502,13 @@
       <c r="AF69" s="185"/>
       <c r="AG69" s="185"/>
       <c r="AH69" s="135">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI69" s="135">
         <v>8</v>
       </c>
       <c r="AJ69" s="223">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:37" customHeight="1" ht="14.25">
@@ -6615,13 +6659,13 @@
       <c r="AF73" s="183"/>
       <c r="AG73" s="183"/>
       <c r="AH73" s="252">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="AI73" s="252">
         <v>5.7</v>
       </c>
       <c r="AJ73" s="104">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="74" spans="1:37" customHeight="1" ht="16.5">
@@ -6657,13 +6701,13 @@
       <c r="AF74" s="173"/>
       <c r="AG74" s="173"/>
       <c r="AH74" s="171">
-        <v>87.7</v>
+        <v>79.9</v>
       </c>
       <c r="AI74" s="136">
         <v>71.6</v>
       </c>
       <c r="AJ74" s="165">
-        <v>83.6</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="75" spans="1:37" customHeight="1" ht="15.75">
@@ -6732,13 +6776,13 @@
       <c r="AF76" s="173"/>
       <c r="AG76" s="173"/>
       <c r="AH76" s="253">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AI76" s="254">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AJ76" s="255">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:37" customHeight="1" ht="16.5">
